--- a/OrganizedData/2025_organized/SpecimenDimensions2025.xlsx
+++ b/OrganizedData/2025_organized/SpecimenDimensions2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F84996E-B75F-4DBF-932D-E9618E5392F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF2ABC59-8A90-492A-9087-E808305F45EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15630" yWindow="2925" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-43770" yWindow="780" windowWidth="21600" windowHeight="13185" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="batch1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="838" uniqueCount="16">
   <si>
     <t>Section</t>
   </si>
@@ -73,9 +73,6 @@
   </si>
   <si>
     <t>TENSION</t>
-  </si>
-  <si>
-    <t>s</t>
   </si>
 </sst>
 </file>
@@ -451,12 +448,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K193"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="11" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -491,7 +488,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>10448</v>
       </c>
@@ -511,7 +508,7 @@
         <v>12.92</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>10448</v>
       </c>
@@ -531,7 +528,7 @@
         <v>12.85</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>10448</v>
       </c>
@@ -557,7 +554,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>10448</v>
       </c>
@@ -583,7 +580,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>10448</v>
       </c>
@@ -609,7 +606,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>10448</v>
       </c>
@@ -635,7 +632,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>10448</v>
       </c>
@@ -661,7 +658,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>10448</v>
       </c>
@@ -687,7 +684,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>10448</v>
       </c>
@@ -712,11 +709,8 @@
       <c r="H10">
         <v>0.7</v>
       </c>
-      <c r="K10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10448</v>
       </c>
@@ -742,7 +736,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>10448</v>
       </c>
@@ -765,7 +759,7 @@
         <v>100.69</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>10448</v>
       </c>
@@ -788,7 +782,7 @@
         <v>91.2</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>10451</v>
       </c>
@@ -808,7 +802,7 @@
         <v>11.54</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>10451</v>
       </c>
@@ -828,7 +822,7 @@
         <v>12.84</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>10451</v>
       </c>
@@ -854,7 +848,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>10451</v>
       </c>
@@ -880,7 +874,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>10451</v>
       </c>
@@ -906,7 +900,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>10451</v>
       </c>
@@ -932,7 +926,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>10451</v>
       </c>
@@ -958,7 +952,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>10451</v>
       </c>
@@ -984,7 +978,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>10451</v>
       </c>
@@ -1010,7 +1004,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>10451</v>
       </c>
@@ -1036,7 +1030,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>10451</v>
       </c>
@@ -1059,7 +1053,7 @@
         <v>73.67</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>10451</v>
       </c>
@@ -1082,7 +1076,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>10444</v>
       </c>
@@ -1102,7 +1096,7 @@
         <v>12.98</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>10444</v>
       </c>
@@ -1122,7 +1116,7 @@
         <v>12.8367</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>10444</v>
       </c>
@@ -1148,7 +1142,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>10444</v>
       </c>
@@ -1174,7 +1168,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>10444</v>
       </c>
@@ -1200,7 +1194,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>10444</v>
       </c>
@@ -1226,7 +1220,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>10444</v>
       </c>
@@ -1252,7 +1246,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>10444</v>
       </c>
@@ -1278,7 +1272,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>10444</v>
       </c>
@@ -1304,7 +1298,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>10444</v>
       </c>
@@ -1330,7 +1324,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>10444</v>
       </c>
@@ -1353,7 +1347,7 @@
         <v>104.93</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>10444</v>
       </c>
@@ -1376,7 +1370,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>10452</v>
       </c>
@@ -1396,7 +1390,7 @@
         <v>12.856</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>10452</v>
       </c>
@@ -1416,7 +1410,7 @@
         <v>13.003</v>
       </c>
     </row>
-    <row r="40" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>10452</v>
       </c>
@@ -1442,7 +1436,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="41" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>10452</v>
       </c>
@@ -1468,7 +1462,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>10452</v>
       </c>
@@ -1494,7 +1488,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="43" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>10452</v>
       </c>
@@ -1520,7 +1514,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="44" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>10452</v>
       </c>
@@ -1546,7 +1540,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="45" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>10452</v>
       </c>
@@ -1572,7 +1566,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="46" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>10452</v>
       </c>
@@ -1598,7 +1592,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>10452</v>
       </c>
@@ -1624,7 +1618,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>10452</v>
       </c>
@@ -1647,7 +1641,7 @@
         <v>83.37</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>10452</v>
       </c>
@@ -1670,7 +1664,7 @@
         <v>84.15</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>10437</v>
       </c>
@@ -1690,7 +1684,7 @@
         <v>12.85</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>10437</v>
       </c>
@@ -1710,7 +1704,7 @@
         <v>12.85</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>10437</v>
       </c>
@@ -1736,7 +1730,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>10437</v>
       </c>
@@ -1762,7 +1756,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>10437</v>
       </c>
@@ -1788,7 +1782,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="55" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>10437</v>
       </c>
@@ -1814,7 +1808,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>10437</v>
       </c>
@@ -1840,7 +1834,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>10437</v>
       </c>
@@ -1866,7 +1860,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>10437</v>
       </c>
@@ -1892,7 +1886,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>10437</v>
       </c>
@@ -1918,7 +1912,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>10437</v>
       </c>
@@ -1941,7 +1935,7 @@
         <v>72.430000000000007</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>10437</v>
       </c>
@@ -1964,7 +1958,7 @@
         <v>67.930000000000007</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>10447</v>
       </c>
@@ -1984,7 +1978,7 @@
         <v>12.77</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>10447</v>
       </c>
@@ -2004,7 +1998,7 @@
         <v>12.85</v>
       </c>
     </row>
-    <row r="64" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>10447</v>
       </c>
@@ -2030,7 +2024,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="65" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>10447</v>
       </c>
@@ -2056,7 +2050,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="66" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>10447</v>
       </c>
@@ -2082,7 +2076,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="67" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>10447</v>
       </c>
@@ -2108,7 +2102,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="68" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>10447</v>
       </c>
@@ -2134,7 +2128,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="69" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>10447</v>
       </c>
@@ -2160,7 +2154,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="70" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>10447</v>
       </c>
@@ -2186,7 +2180,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="71" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>10447</v>
       </c>
@@ -2212,7 +2206,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="72" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>10447</v>
       </c>
@@ -2235,7 +2229,7 @@
         <v>96.5</v>
       </c>
     </row>
-    <row r="73" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>10447</v>
       </c>
@@ -2258,7 +2252,7 @@
         <v>97.16</v>
       </c>
     </row>
-    <row r="74" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>10453</v>
       </c>
@@ -2278,7 +2272,7 @@
         <v>12.69</v>
       </c>
     </row>
-    <row r="75" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>10453</v>
       </c>
@@ -2298,7 +2292,7 @@
         <v>12.85</v>
       </c>
     </row>
-    <row r="76" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>10453</v>
       </c>
@@ -2324,7 +2318,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="77" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>10453</v>
       </c>
@@ -2350,7 +2344,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="78" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>10453</v>
       </c>
@@ -2376,7 +2370,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="79" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>10453</v>
       </c>
@@ -2402,7 +2396,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="80" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>10453</v>
       </c>
@@ -2428,7 +2422,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="81" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>10453</v>
       </c>
@@ -2454,7 +2448,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="82" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>10453</v>
       </c>
@@ -2480,7 +2474,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="83" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>10453</v>
       </c>
@@ -2506,7 +2500,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="84" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>10453</v>
       </c>
@@ -2529,7 +2523,7 @@
         <v>79.5</v>
       </c>
     </row>
-    <row r="85" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>10453</v>
       </c>
@@ -2552,7 +2546,7 @@
         <v>84.97</v>
       </c>
     </row>
-    <row r="86" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>10441</v>
       </c>
@@ -2572,7 +2566,7 @@
         <v>12.82</v>
       </c>
     </row>
-    <row r="87" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>10441</v>
       </c>
@@ -2592,7 +2586,7 @@
         <v>12.83</v>
       </c>
     </row>
-    <row r="88" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>10441</v>
       </c>
@@ -2618,7 +2612,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="89" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>10441</v>
       </c>
@@ -2644,7 +2638,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="90" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>10441</v>
       </c>
@@ -2670,7 +2664,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="91" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>10441</v>
       </c>
@@ -2696,7 +2690,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="92" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>10441</v>
       </c>
@@ -2722,7 +2716,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="93" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>10441</v>
       </c>
@@ -2748,7 +2742,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="94" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>10441</v>
       </c>
@@ -2774,7 +2768,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="95" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>10441</v>
       </c>
@@ -2800,7 +2794,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="96" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>10441</v>
       </c>
@@ -2823,7 +2817,7 @@
         <v>65.093299999999999</v>
       </c>
     </row>
-    <row r="97" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>10441</v>
       </c>
@@ -2846,7 +2840,7 @@
         <v>66.86</v>
       </c>
     </row>
-    <row r="98" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>10440</v>
       </c>
@@ -2866,7 +2860,7 @@
         <v>12.77</v>
       </c>
     </row>
-    <row r="99" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>10440</v>
       </c>
@@ -2886,7 +2880,7 @@
         <v>12.85</v>
       </c>
     </row>
-    <row r="100" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>10440</v>
       </c>
@@ -2912,7 +2906,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="101" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>10440</v>
       </c>
@@ -2938,7 +2932,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="102" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>10440</v>
       </c>
@@ -2964,7 +2958,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="103" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>10440</v>
       </c>
@@ -2990,7 +2984,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="104" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>10440</v>
       </c>
@@ -3016,7 +3010,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="105" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>10440</v>
       </c>
@@ -3042,7 +3036,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="106" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>10440</v>
       </c>
@@ -3068,7 +3062,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="107" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>10440</v>
       </c>
@@ -3094,7 +3088,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="108" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>10440</v>
       </c>
@@ -3117,7 +3111,7 @@
         <v>83.16</v>
       </c>
     </row>
-    <row r="109" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>10440</v>
       </c>
@@ -3140,7 +3134,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="110" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>10435</v>
       </c>
@@ -3160,7 +3154,7 @@
         <v>12.85</v>
       </c>
     </row>
-    <row r="111" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>10435</v>
       </c>
@@ -3180,7 +3174,7 @@
         <v>13.04</v>
       </c>
     </row>
-    <row r="112" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>10435</v>
       </c>
@@ -3206,7 +3200,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="113" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A113">
         <v>10435</v>
       </c>
@@ -3232,7 +3226,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="114" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A114">
         <v>10435</v>
       </c>
@@ -3258,7 +3252,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="115" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A115">
         <v>10435</v>
       </c>
@@ -3284,7 +3278,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="116" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A116">
         <v>10435</v>
       </c>
@@ -3310,7 +3304,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="117" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A117">
         <v>10435</v>
       </c>
@@ -3336,7 +3330,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="118" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A118">
         <v>10435</v>
       </c>
@@ -3362,7 +3356,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="119" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A119">
         <v>10435</v>
       </c>
@@ -3388,7 +3382,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="120" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A120">
         <v>10435</v>
       </c>
@@ -3411,7 +3405,7 @@
         <v>73.400000000000006</v>
       </c>
     </row>
-    <row r="121" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A121">
         <v>10435</v>
       </c>
@@ -3434,7 +3428,7 @@
         <v>73.66</v>
       </c>
     </row>
-    <row r="122" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A122">
         <v>10446</v>
       </c>
@@ -3454,7 +3448,7 @@
         <v>12.576000000000001</v>
       </c>
     </row>
-    <row r="123" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A123">
         <v>10446</v>
       </c>
@@ -3474,7 +3468,7 @@
         <v>12.836</v>
       </c>
     </row>
-    <row r="124" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A124">
         <v>10446</v>
       </c>
@@ -3500,7 +3494,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="125" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A125">
         <v>10446</v>
       </c>
@@ -3526,7 +3520,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="126" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A126">
         <v>10446</v>
       </c>
@@ -3552,7 +3546,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="127" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A127">
         <v>10446</v>
       </c>
@@ -3578,7 +3572,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="128" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A128">
         <v>10446</v>
       </c>
@@ -3604,7 +3598,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="129" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A129">
         <v>10446</v>
       </c>
@@ -3630,7 +3624,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="130" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A130">
         <v>10446</v>
       </c>
@@ -3656,7 +3650,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="131" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A131">
         <v>10446</v>
       </c>
@@ -3682,7 +3676,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A132">
         <v>10446</v>
       </c>
@@ -3705,7 +3699,7 @@
         <v>70.72</v>
       </c>
     </row>
-    <row r="133" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A133">
         <v>10446</v>
       </c>
@@ -3728,7 +3722,7 @@
         <v>71.62</v>
       </c>
     </row>
-    <row r="134" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A134">
         <v>10436</v>
       </c>
@@ -3748,7 +3742,7 @@
         <v>12.872999999999999</v>
       </c>
     </row>
-    <row r="135" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A135">
         <v>10436</v>
       </c>
@@ -3768,7 +3762,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="136" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A136">
         <v>10436</v>
       </c>
@@ -3794,7 +3788,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="137" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A137">
         <v>10436</v>
       </c>
@@ -3820,7 +3814,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="138" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A138">
         <v>10436</v>
       </c>
@@ -3846,7 +3840,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="139" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A139">
         <v>10436</v>
       </c>
@@ -3872,7 +3866,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="140" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A140">
         <v>10436</v>
       </c>
@@ -3898,7 +3892,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="141" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A141">
         <v>10436</v>
       </c>
@@ -3924,7 +3918,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="142" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A142">
         <v>10436</v>
       </c>
@@ -3950,7 +3944,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="143" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A143">
         <v>10436</v>
       </c>
@@ -3976,7 +3970,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="144" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A144">
         <v>10436</v>
       </c>
@@ -3999,7 +3993,7 @@
         <v>66.866</v>
       </c>
     </row>
-    <row r="145" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A145">
         <v>10436</v>
       </c>
@@ -4022,7 +4016,7 @@
         <v>67.87</v>
       </c>
     </row>
-    <row r="146" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A146">
         <v>10450</v>
       </c>
@@ -4042,7 +4036,7 @@
         <v>12.88</v>
       </c>
     </row>
-    <row r="147" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A147">
         <v>10450</v>
       </c>
@@ -4062,7 +4056,7 @@
         <v>12.91</v>
       </c>
     </row>
-    <row r="148" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A148">
         <v>10450</v>
       </c>
@@ -4088,7 +4082,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="149" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A149">
         <v>10450</v>
       </c>
@@ -4114,7 +4108,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="150" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A150">
         <v>10450</v>
       </c>
@@ -4140,7 +4134,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="151" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A151">
         <v>10450</v>
       </c>
@@ -4166,7 +4160,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="152" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A152">
         <v>10450</v>
       </c>
@@ -4192,7 +4186,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="153" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A153">
         <v>10450</v>
       </c>
@@ -4218,7 +4212,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="154" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A154">
         <v>10450</v>
       </c>
@@ -4244,7 +4238,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="155" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A155">
         <v>10450</v>
       </c>
@@ -4270,7 +4264,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="156" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A156">
         <v>10450</v>
       </c>
@@ -4293,7 +4287,7 @@
         <v>71.453000000000003</v>
       </c>
     </row>
-    <row r="157" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A157">
         <v>10450</v>
       </c>
@@ -4316,7 +4310,7 @@
         <v>76.712999999999994</v>
       </c>
     </row>
-    <row r="158" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A158">
         <v>10438</v>
       </c>
@@ -4336,7 +4330,7 @@
         <v>12.92</v>
       </c>
     </row>
-    <row r="159" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A159">
         <v>10438</v>
       </c>
@@ -4356,7 +4350,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="160" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A160">
         <v>10438</v>
       </c>
@@ -4382,7 +4376,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="161" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A161">
         <v>10438</v>
       </c>
@@ -4408,7 +4402,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="162" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A162">
         <v>10438</v>
       </c>
@@ -4434,7 +4428,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A163">
         <v>10438</v>
       </c>
@@ -4460,7 +4454,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="164" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A164">
         <v>10438</v>
       </c>
@@ -4486,7 +4480,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="165" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A165">
         <v>10438</v>
       </c>
@@ -4512,7 +4506,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="166" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A166">
         <v>10438</v>
       </c>
@@ -4538,7 +4532,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="167" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A167">
         <v>10438</v>
       </c>
@@ -4564,7 +4558,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="168" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A168">
         <v>10438</v>
       </c>
@@ -4587,7 +4581,7 @@
         <v>74.260000000000005</v>
       </c>
     </row>
-    <row r="169" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A169">
         <v>10438</v>
       </c>
@@ -4610,7 +4604,7 @@
         <v>78.22</v>
       </c>
     </row>
-    <row r="170" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A170">
         <v>10454</v>
       </c>
@@ -4630,7 +4624,7 @@
         <v>12.52</v>
       </c>
     </row>
-    <row r="171" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A171">
         <v>10454</v>
       </c>
@@ -4650,7 +4644,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="172" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A172">
         <v>10454</v>
       </c>
@@ -4676,7 +4670,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="173" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A173">
         <v>10454</v>
       </c>
@@ -4702,7 +4696,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="174" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A174">
         <v>10454</v>
       </c>
@@ -4728,7 +4722,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="175" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A175">
         <v>10454</v>
       </c>
@@ -4754,7 +4748,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="176" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A176">
         <v>10454</v>
       </c>
@@ -4780,7 +4774,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="177" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A177">
         <v>10454</v>
       </c>
@@ -4806,7 +4800,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="178" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A178">
         <v>10454</v>
       </c>
@@ -4832,7 +4826,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="179" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A179">
         <v>10454</v>
       </c>
@@ -4858,7 +4852,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="180" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A180">
         <v>10454</v>
       </c>
@@ -4881,7 +4875,7 @@
         <v>101.09</v>
       </c>
     </row>
-    <row r="181" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A181">
         <v>10454</v>
       </c>
@@ -5207,12 +5201,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K217"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="11" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5247,7 +5241,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>10453</v>
       </c>
@@ -5267,7 +5261,7 @@
         <v>12.69</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>10453</v>
       </c>
@@ -5287,7 +5281,7 @@
         <v>12.85</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>10453</v>
       </c>
@@ -5313,7 +5307,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>10453</v>
       </c>
@@ -5339,7 +5333,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>10453</v>
       </c>
@@ -5365,7 +5359,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>10453</v>
       </c>
@@ -5391,7 +5385,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>10453</v>
       </c>
@@ -5417,7 +5411,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>10453</v>
       </c>
@@ -5443,7 +5437,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>10453</v>
       </c>
@@ -5469,7 +5463,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10453</v>
       </c>
@@ -5495,7 +5489,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>10453</v>
       </c>
@@ -5518,7 +5512,7 @@
         <v>79.5</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>10453</v>
       </c>
@@ -5541,7 +5535,7 @@
         <v>84.97</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>10451</v>
       </c>
@@ -5561,7 +5555,7 @@
         <v>13.23</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>10451</v>
       </c>
@@ -5581,7 +5575,7 @@
         <v>12.86</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>10451</v>
       </c>
@@ -5607,7 +5601,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>10451</v>
       </c>
@@ -5633,7 +5627,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>10451</v>
       </c>
@@ -5659,7 +5653,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>10451</v>
       </c>
@@ -5685,7 +5679,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>10451</v>
       </c>
@@ -5711,7 +5705,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>10451</v>
       </c>
@@ -5737,7 +5731,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>10451</v>
       </c>
@@ -5763,7 +5757,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>10451</v>
       </c>
@@ -5789,7 +5783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>10451</v>
       </c>
@@ -5812,7 +5806,7 @@
         <v>78.326999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>10451</v>
       </c>
@@ -5835,7 +5829,7 @@
         <v>80.63</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>10444</v>
       </c>
@@ -5855,7 +5849,7 @@
         <v>12.88</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>10444</v>
       </c>
@@ -5875,7 +5869,7 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>10444</v>
       </c>
@@ -5901,7 +5895,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>10444</v>
       </c>
@@ -5927,7 +5921,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>10444</v>
       </c>
@@ -5953,7 +5947,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>10444</v>
       </c>
@@ -5979,7 +5973,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>10444</v>
       </c>
@@ -6005,7 +5999,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>10444</v>
       </c>
@@ -6031,7 +6025,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>10444</v>
       </c>
@@ -6057,7 +6051,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>10444</v>
       </c>
@@ -6083,7 +6077,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>10444</v>
       </c>
@@ -6106,7 +6100,7 @@
         <v>91.38</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>10444</v>
       </c>
@@ -6129,7 +6123,7 @@
         <v>89.89</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>10452</v>
       </c>
@@ -6149,7 +6143,7 @@
         <v>12.89</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>10452</v>
       </c>
@@ -6169,7 +6163,7 @@
         <v>12.84</v>
       </c>
     </row>
-    <row r="40" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>10452</v>
       </c>
@@ -6195,7 +6189,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="41" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>10452</v>
       </c>
@@ -6221,7 +6215,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>10452</v>
       </c>
@@ -6247,7 +6241,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="43" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>10452</v>
       </c>
@@ -6273,7 +6267,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="44" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>10452</v>
       </c>
@@ -6299,7 +6293,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="45" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>10452</v>
       </c>
@@ -6325,7 +6319,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="46" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>10452</v>
       </c>
@@ -6351,7 +6345,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>10452</v>
       </c>
@@ -6377,7 +6371,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>10452</v>
       </c>
@@ -6400,7 +6394,7 @@
         <v>66.44</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>10452</v>
       </c>
@@ -6423,7 +6417,7 @@
         <v>66.489999999999995</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>10447</v>
       </c>
@@ -6443,7 +6437,7 @@
         <v>12.87</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>10447</v>
       </c>
@@ -6463,7 +6457,7 @@
         <v>12.98</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>10447</v>
       </c>
@@ -6489,7 +6483,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>10447</v>
       </c>
@@ -6515,7 +6509,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>10447</v>
       </c>
@@ -6541,7 +6535,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="55" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>10447</v>
       </c>
@@ -6567,7 +6561,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>10447</v>
       </c>
@@ -6593,7 +6587,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>10447</v>
       </c>
@@ -6619,7 +6613,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>10447</v>
       </c>
@@ -6645,7 +6639,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>10447</v>
       </c>
@@ -6671,7 +6665,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>10447</v>
       </c>
@@ -6694,7 +6688,7 @@
         <v>78.33</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>10447</v>
       </c>
@@ -6717,7 +6711,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>10441</v>
       </c>
@@ -6737,7 +6731,7 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>10441</v>
       </c>
@@ -6757,7 +6751,7 @@
         <v>12.87</v>
       </c>
     </row>
-    <row r="64" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>10441</v>
       </c>
@@ -6783,7 +6777,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="65" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>10441</v>
       </c>
@@ -6809,7 +6803,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="66" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>10441</v>
       </c>
@@ -6835,7 +6829,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>10441</v>
       </c>
@@ -6861,7 +6855,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="68" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>10441</v>
       </c>
@@ -6887,7 +6881,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="69" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>10441</v>
       </c>
@@ -6913,7 +6907,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="70" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>10441</v>
       </c>
@@ -6939,7 +6933,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="71" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>10441</v>
       </c>
@@ -6965,7 +6959,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="72" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>10441</v>
       </c>
@@ -6988,7 +6982,7 @@
         <v>64.97</v>
       </c>
     </row>
-    <row r="73" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>10441</v>
       </c>
@@ -7011,7 +7005,7 @@
         <v>65.78</v>
       </c>
     </row>
-    <row r="74" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>10440</v>
       </c>
@@ -7031,7 +7025,7 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="75" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>10440</v>
       </c>
@@ -7051,7 +7045,7 @@
         <v>13.03</v>
       </c>
     </row>
-    <row r="76" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>10440</v>
       </c>
@@ -7077,7 +7071,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="77" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>10440</v>
       </c>
@@ -7103,7 +7097,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="78" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>10440</v>
       </c>
@@ -7129,7 +7123,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="79" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>10440</v>
       </c>
@@ -7155,7 +7149,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="80" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>10440</v>
       </c>
@@ -7181,7 +7175,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="81" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>10440</v>
       </c>
@@ -7207,7 +7201,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="82" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>10440</v>
       </c>
@@ -7233,7 +7227,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="83" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>10440</v>
       </c>
@@ -7259,7 +7253,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="84" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>10440</v>
       </c>
@@ -7282,7 +7276,7 @@
         <v>78.3</v>
       </c>
     </row>
-    <row r="85" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>10440</v>
       </c>
@@ -7305,7 +7299,7 @@
         <v>78.3</v>
       </c>
     </row>
-    <row r="86" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>10435</v>
       </c>
@@ -7325,7 +7319,7 @@
         <v>12.85</v>
       </c>
     </row>
-    <row r="87" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>10435</v>
       </c>
@@ -7345,7 +7339,7 @@
         <v>13.04</v>
       </c>
     </row>
-    <row r="88" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>10435</v>
       </c>
@@ -7371,7 +7365,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="89" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>10435</v>
       </c>
@@ -7397,7 +7391,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="90" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>10435</v>
       </c>
@@ -7423,7 +7417,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="91" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>10435</v>
       </c>
@@ -7449,7 +7443,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="92" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>10435</v>
       </c>
@@ -7475,7 +7469,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="93" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>10435</v>
       </c>
@@ -7501,7 +7495,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="94" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>10435</v>
       </c>
@@ -7527,7 +7521,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="95" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>10435</v>
       </c>
@@ -7553,7 +7547,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="96" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>10435</v>
       </c>
@@ -7576,7 +7570,7 @@
         <v>73.400000000000006</v>
       </c>
     </row>
-    <row r="97" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>10435</v>
       </c>
@@ -7599,7 +7593,7 @@
         <v>73.66</v>
       </c>
     </row>
-    <row r="98" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>10437</v>
       </c>
@@ -7619,7 +7613,7 @@
         <v>12.73</v>
       </c>
     </row>
-    <row r="99" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>10437</v>
       </c>
@@ -7639,7 +7633,7 @@
         <v>13.01</v>
       </c>
     </row>
-    <row r="100" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>10437</v>
       </c>
@@ -7665,7 +7659,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="101" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>10437</v>
       </c>
@@ -7691,7 +7685,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="102" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>10437</v>
       </c>
@@ -7717,7 +7711,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="103" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>10437</v>
       </c>
@@ -7743,7 +7737,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="104" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>10437</v>
       </c>
@@ -7769,7 +7763,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="105" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>10437</v>
       </c>
@@ -7795,7 +7789,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="106" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>10437</v>
       </c>
@@ -7821,7 +7815,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="107" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>10437</v>
       </c>
@@ -7847,7 +7841,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="108" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>10437</v>
       </c>
@@ -7870,7 +7864,7 @@
         <v>71.83</v>
       </c>
     </row>
-    <row r="109" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>10437</v>
       </c>
@@ -7893,7 +7887,7 @@
         <v>72.709999999999994</v>
       </c>
     </row>
-    <row r="110" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>10446</v>
       </c>
@@ -7913,7 +7907,7 @@
         <v>12.89</v>
       </c>
     </row>
-    <row r="111" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>10446</v>
       </c>
@@ -7933,7 +7927,7 @@
         <v>12.99</v>
       </c>
     </row>
-    <row r="112" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>10446</v>
       </c>
@@ -7959,7 +7953,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="113" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A113">
         <v>10446</v>
       </c>
@@ -7985,7 +7979,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="114" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A114">
         <v>10446</v>
       </c>
@@ -8011,7 +8005,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="115" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A115">
         <v>10446</v>
       </c>
@@ -8037,7 +8031,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="116" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A116">
         <v>10446</v>
       </c>
@@ -8063,7 +8057,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="117" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A117">
         <v>10446</v>
       </c>
@@ -8089,7 +8083,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="118" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A118">
         <v>10446</v>
       </c>
@@ -8115,7 +8109,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="119" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A119">
         <v>10446</v>
       </c>
@@ -8141,7 +8135,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="120" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A120">
         <v>10446</v>
       </c>
@@ -8164,7 +8158,7 @@
         <v>77.83</v>
       </c>
     </row>
-    <row r="121" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A121">
         <v>10446</v>
       </c>
@@ -8187,7 +8181,7 @@
         <v>79.36</v>
       </c>
     </row>
-    <row r="122" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A122">
         <v>10436</v>
       </c>
@@ -8207,7 +8201,7 @@
         <v>12.91</v>
       </c>
     </row>
-    <row r="123" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A123">
         <v>10436</v>
       </c>
@@ -8227,7 +8221,7 @@
         <v>13.01</v>
       </c>
     </row>
-    <row r="124" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A124">
         <v>10436</v>
       </c>
@@ -8253,7 +8247,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="125" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A125">
         <v>10436</v>
       </c>
@@ -8279,7 +8273,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="126" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A126">
         <v>10436</v>
       </c>
@@ -8305,7 +8299,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="127" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A127">
         <v>10436</v>
       </c>
@@ -8331,7 +8325,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="128" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A128">
         <v>10436</v>
       </c>
@@ -8357,7 +8351,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="129" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A129">
         <v>10436</v>
       </c>
@@ -8383,7 +8377,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="130" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A130">
         <v>10436</v>
       </c>
@@ -8409,7 +8403,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="131" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A131">
         <v>10436</v>
       </c>
@@ -8435,7 +8429,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="132" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A132">
         <v>10436</v>
       </c>
@@ -8458,7 +8452,7 @@
         <v>68.58</v>
       </c>
     </row>
-    <row r="133" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A133">
         <v>10436</v>
       </c>
@@ -8481,7 +8475,7 @@
         <v>70.56</v>
       </c>
     </row>
-    <row r="134" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A134">
         <v>10450</v>
       </c>
@@ -8501,7 +8495,7 @@
         <v>12.83</v>
       </c>
     </row>
-    <row r="135" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A135">
         <v>10450</v>
       </c>
@@ -8521,7 +8515,7 @@
         <v>13.09</v>
       </c>
     </row>
-    <row r="136" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A136">
         <v>10450</v>
       </c>
@@ -8547,7 +8541,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="137" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A137">
         <v>10450</v>
       </c>
@@ -8573,7 +8567,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="138" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A138">
         <v>10450</v>
       </c>
@@ -8599,7 +8593,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="139" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A139">
         <v>10450</v>
       </c>
@@ -8625,7 +8619,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="140" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A140">
         <v>10450</v>
       </c>
@@ -8651,7 +8645,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="141" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A141">
         <v>10450</v>
       </c>
@@ -8677,7 +8671,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="142" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A142">
         <v>10450</v>
       </c>
@@ -8703,7 +8697,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="143" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A143">
         <v>10450</v>
       </c>
@@ -8729,7 +8723,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A144">
         <v>10450</v>
       </c>
@@ -8752,7 +8746,7 @@
         <v>84.92</v>
       </c>
     </row>
-    <row r="145" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A145">
         <v>10450</v>
       </c>
@@ -8775,7 +8769,7 @@
         <v>87.29</v>
       </c>
     </row>
-    <row r="146" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A146">
         <v>10448</v>
       </c>
@@ -8795,7 +8789,7 @@
         <v>12.98</v>
       </c>
     </row>
-    <row r="147" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A147">
         <v>10448</v>
       </c>
@@ -8815,7 +8809,7 @@
         <v>12.77</v>
       </c>
     </row>
-    <row r="148" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A148">
         <v>10448</v>
       </c>
@@ -8841,7 +8835,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="149" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A149">
         <v>10448</v>
       </c>
@@ -8867,7 +8861,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="150" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A150">
         <v>10448</v>
       </c>
@@ -8893,7 +8887,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="151" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A151">
         <v>10448</v>
       </c>
@@ -8919,7 +8913,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="152" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A152">
         <v>10448</v>
       </c>
@@ -8945,7 +8939,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="153" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A153">
         <v>10448</v>
       </c>
@@ -8971,7 +8965,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="154" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A154">
         <v>10448</v>
       </c>
@@ -8997,7 +8991,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="155" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A155">
         <v>10448</v>
       </c>
@@ -9023,7 +9017,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="156" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A156">
         <v>10448</v>
       </c>
@@ -9046,7 +9040,7 @@
         <v>97.59</v>
       </c>
     </row>
-    <row r="157" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A157">
         <v>10448</v>
       </c>
@@ -9069,7 +9063,7 @@
         <v>104.76</v>
       </c>
     </row>
-    <row r="158" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A158">
         <v>80463</v>
       </c>
@@ -9089,7 +9083,7 @@
         <v>12.98</v>
       </c>
     </row>
-    <row r="159" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A159">
         <v>80463</v>
       </c>
@@ -9109,7 +9103,7 @@
         <v>12.77</v>
       </c>
     </row>
-    <row r="160" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A160">
         <v>80463</v>
       </c>
@@ -9135,7 +9129,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="161" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A161">
         <v>80463</v>
       </c>
@@ -9161,7 +9155,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="162" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A162">
         <v>80463</v>
       </c>
@@ -9187,7 +9181,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="163" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A163">
         <v>80463</v>
       </c>
@@ -9213,7 +9207,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="164" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A164">
         <v>80463</v>
       </c>
@@ -9239,7 +9233,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="165" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A165">
         <v>80463</v>
       </c>
@@ -9265,7 +9259,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="166" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A166">
         <v>80463</v>
       </c>
@@ -9291,7 +9285,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="167" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A167">
         <v>80463</v>
       </c>
@@ -9317,7 +9311,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="168" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A168">
         <v>80463</v>
       </c>
@@ -9340,7 +9334,7 @@
         <v>97.59</v>
       </c>
     </row>
-    <row r="169" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A169">
         <v>80463</v>
       </c>
@@ -9363,7 +9357,7 @@
         <v>104.76</v>
       </c>
     </row>
-    <row r="170" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A170">
         <v>91284</v>
       </c>
@@ -9383,7 +9377,7 @@
         <v>12.98</v>
       </c>
     </row>
-    <row r="171" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A171">
         <v>91284</v>
       </c>
@@ -9403,7 +9397,7 @@
         <v>12.77</v>
       </c>
     </row>
-    <row r="172" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A172">
         <v>91284</v>
       </c>
@@ -9429,7 +9423,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="173" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A173">
         <v>91284</v>
       </c>
@@ -9455,7 +9449,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="174" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A174">
         <v>91284</v>
       </c>
@@ -9481,7 +9475,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="175" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A175">
         <v>91284</v>
       </c>
@@ -9507,7 +9501,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="176" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A176">
         <v>91284</v>
       </c>
@@ -9533,7 +9527,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="177" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A177">
         <v>91284</v>
       </c>
@@ -9559,7 +9553,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="178" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A178">
         <v>91284</v>
       </c>
@@ -9585,7 +9579,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="179" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A179">
         <v>91284</v>
       </c>
@@ -9611,7 +9605,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="180" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A180">
         <v>91284</v>
       </c>
@@ -9634,7 +9628,7 @@
         <v>97.59</v>
       </c>
     </row>
-    <row r="181" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A181">
         <v>91284</v>
       </c>
@@ -9657,7 +9651,7 @@
         <v>104.76</v>
       </c>
     </row>
-    <row r="182" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A182">
         <v>80464</v>
       </c>
@@ -9677,7 +9671,7 @@
         <v>12.98</v>
       </c>
     </row>
-    <row r="183" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A183">
         <v>80464</v>
       </c>
@@ -9697,7 +9691,7 @@
         <v>12.77</v>
       </c>
     </row>
-    <row r="184" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A184">
         <v>80464</v>
       </c>
@@ -9723,7 +9717,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="185" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A185">
         <v>80464</v>
       </c>
@@ -9749,7 +9743,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="186" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A186">
         <v>80464</v>
       </c>
@@ -9775,7 +9769,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="187" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A187">
         <v>80464</v>
       </c>
@@ -9801,7 +9795,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="188" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A188">
         <v>80464</v>
       </c>
@@ -9827,7 +9821,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="189" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A189">
         <v>80464</v>
       </c>
@@ -9853,7 +9847,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="190" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A190">
         <v>80464</v>
       </c>
@@ -9879,7 +9873,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="191" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A191">
         <v>80464</v>
       </c>
@@ -9905,7 +9899,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="192" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A192">
         <v>80464</v>
       </c>
@@ -9928,7 +9922,7 @@
         <v>97.59</v>
       </c>
     </row>
-    <row r="193" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A193">
         <v>80464</v>
       </c>
@@ -9951,7 +9945,7 @@
         <v>104.76</v>
       </c>
     </row>
-    <row r="194" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A194">
         <v>10438</v>
       </c>
@@ -9971,7 +9965,7 @@
         <v>12.84</v>
       </c>
     </row>
-    <row r="195" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A195">
         <v>10438</v>
       </c>
@@ -9991,7 +9985,7 @@
         <v>13.01</v>
       </c>
     </row>
-    <row r="196" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A196">
         <v>10438</v>
       </c>
@@ -10017,7 +10011,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="197" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A197">
         <v>10438</v>
       </c>
@@ -10043,7 +10037,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="198" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A198">
         <v>10438</v>
       </c>
@@ -10069,7 +10063,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="199" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A199">
         <v>10438</v>
       </c>
@@ -10095,7 +10089,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="200" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A200">
         <v>10438</v>
       </c>
@@ -10121,7 +10115,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="201" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A201">
         <v>10438</v>
       </c>
@@ -10147,7 +10141,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="202" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A202">
         <v>10438</v>
       </c>
@@ -10173,7 +10167,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="203" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A203">
         <v>10438</v>
       </c>
@@ -10199,7 +10193,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="204" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A204">
         <v>10438</v>
       </c>
@@ -10222,7 +10216,7 @@
         <v>70.3</v>
       </c>
     </row>
-    <row r="205" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A205">
         <v>10438</v>
       </c>
@@ -10245,7 +10239,7 @@
         <v>78.989999999999995</v>
       </c>
     </row>
-    <row r="206" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A206">
         <v>10454</v>
       </c>
@@ -10265,7 +10259,7 @@
         <v>12.72</v>
       </c>
     </row>
-    <row r="207" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A207">
         <v>10454</v>
       </c>
@@ -10285,7 +10279,7 @@
         <v>12.99</v>
       </c>
     </row>
-    <row r="208" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A208">
         <v>10454</v>
       </c>
@@ -10311,7 +10305,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="209" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A209">
         <v>10454</v>
       </c>
@@ -10337,7 +10331,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="210" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A210">
         <v>10454</v>
       </c>
@@ -10363,7 +10357,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="211" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A211">
         <v>10454</v>
       </c>
@@ -10389,7 +10383,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="212" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A212">
         <v>10454</v>
       </c>
@@ -10415,7 +10409,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="213" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A213">
         <v>10454</v>
       </c>
@@ -10441,7 +10435,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="214" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A214">
         <v>10454</v>
       </c>
@@ -10467,7 +10461,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="215" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A215">
         <v>10454</v>
       </c>
@@ -10493,7 +10487,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A216">
         <v>10454</v>
       </c>
@@ -10516,7 +10510,7 @@
         <v>69.86</v>
       </c>
     </row>
-    <row r="217" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A217">
         <v>10454</v>
       </c>
